--- a/masters/templates/SALES ORDER.xlsx
+++ b/masters/templates/SALES ORDER.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\vibe-coding\po2sap\samples\templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\vibe-coding\po2sap\masters\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC5714EB-D343-4060-9EC3-BF58767A604B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{946B600B-6571-4606-B83F-F9E8073D4211}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{79E9F20C-1732-4EAD-88AB-1A016E0EA9D1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{79E9F20C-1732-4EAD-88AB-1A016E0EA9D1}"/>
   </bookViews>
   <sheets>
     <sheet name="SALES ORDER" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="57">
   <si>
     <t>SALES ORDER TYPE</t>
   </si>
@@ -185,6 +185,14 @@
   </si>
   <si>
     <t>VGPOS</t>
+  </si>
+  <si>
+    <t>YOUR CODE</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>KDMAT</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1138,10 +1146,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{083F5578-518F-4A75-BDB4-C83502DFD789}">
-  <dimension ref="A1:AB2"/>
+  <dimension ref="A1:AC2"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1161,73 +1169,76 @@
         <v>5</v>
       </c>
       <c r="G1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
+        <v>55</v>
+      </c>
+      <c r="O1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="P1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" t="s">
+      <c r="Q1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" t="s">
+      <c r="R1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="S1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" t="s">
+      <c r="T1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" t="s">
+      <c r="U1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" t="s">
+      <c r="V1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" t="s">
+      <c r="W1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" t="s">
-        <v>21</v>
-      </c>
-      <c r="W1" t="s">
+      <c r="X1" t="s">
         <v>22</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Y1" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Z1" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AA1" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AB1" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AC1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>28</v>
       </c>
@@ -1247,69 +1258,72 @@
         <v>33</v>
       </c>
       <c r="G2" t="s">
+        <v>48</v>
+      </c>
+      <c r="H2" t="s">
         <v>34</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>35</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>36</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>37</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>38</v>
       </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
         <v>39</v>
       </c>
-      <c r="M2" t="s">
+      <c r="N2" t="s">
+        <v>56</v>
+      </c>
+      <c r="O2" t="s">
         <v>40</v>
       </c>
-      <c r="N2" t="s">
+      <c r="P2" t="s">
         <v>41</v>
       </c>
-      <c r="O2" t="s">
+      <c r="Q2" t="s">
         <v>42</v>
       </c>
-      <c r="P2" t="s">
+      <c r="R2" t="s">
         <v>43</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="S2" t="s">
         <v>44</v>
       </c>
-      <c r="R2" t="s">
+      <c r="T2" t="s">
         <v>45</v>
       </c>
-      <c r="S2" t="s">
+      <c r="U2" t="s">
         <v>18</v>
       </c>
-      <c r="T2" t="s">
+      <c r="V2" t="s">
         <v>46</v>
       </c>
-      <c r="U2" t="s">
+      <c r="W2" t="s">
         <v>47</v>
       </c>
-      <c r="V2" t="s">
-        <v>48</v>
-      </c>
-      <c r="W2" t="s">
+      <c r="X2" t="s">
         <v>49</v>
       </c>
-      <c r="X2" t="s">
+      <c r="Y2" t="s">
         <v>50</v>
       </c>
-      <c r="Y2" t="s">
+      <c r="Z2" t="s">
         <v>51</v>
       </c>
-      <c r="Z2" t="s">
+      <c r="AA2" t="s">
         <v>52</v>
       </c>
-      <c r="AA2" t="s">
+      <c r="AB2" t="s">
         <v>53</v>
       </c>
-      <c r="AB2" t="s">
+      <c r="AC2" t="s">
         <v>54</v>
       </c>
     </row>
